--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BLACK_BEAR.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BLACK_BEAR.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="135" windowWidth="25170" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2026_BLACK_BEAR" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +12,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_BLACK_BEAR'!$A$3:$N$109</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026_BLACK_BEAR'!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,30 +30,19 @@
     <font>
       <name val="Georgia"/>
       <b val="1"/>
-      <color rgb="003A1D06"/>
+      <color rgb="FF3A1D06"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="005A4737"/>
+      <color rgb="FF5A4737"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="002F2119"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -62,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,27 +59,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6E9D6"/>
+        <fgColor rgb="FFF6E9D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D96F00"/>
+        <fgColor rgb="FFFFF7EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7EC"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F2D1D"/>
+        <fgColor rgb="FF4F2D1D"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,69 +88,47 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B8895F"/>
+        <color rgb="FFB8895F"/>
       </left>
       <right style="thin">
-        <color rgb="00B8895F"/>
+        <color rgb="FFB8895F"/>
       </right>
       <top style="thin">
-        <color rgb="00B8895F"/>
+        <color rgb="FFB8895F"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B8895F"/>
+        <color rgb="FFB8895F"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -242,7 +203,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HUNT_TABLE_005" displayName="HUNT_TABLE_005" ref="A3:N109" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HUNT_TABLE_BLACK_BEAR" displayName="HUNT_TABLE_BLACK_BEAR" ref="A3:N109" headerRowCount="1">
   <autoFilter ref="A3:N109"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Hunt Name"/>
@@ -556,6001 +517,5995 @@
   <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" style="6" min="1" max="1"/>
+    <col width="14" customWidth="1" style="6" min="2" max="4"/>
+    <col width="20" customWidth="1" style="6" min="5" max="5"/>
+    <col width="28" customWidth="1" style="6" min="6" max="6"/>
+    <col width="36" customWidth="1" style="6" min="7" max="7"/>
+    <col width="14" customWidth="1" style="6" min="8" max="10"/>
+    <col width="20" customWidth="1" style="6" min="11" max="11"/>
+    <col width="36" customWidth="1" style="6" min="12" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32.1" customHeight="1" s="6">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>2026 BLACK BEAR</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="33.95" customHeight="1" s="6">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Source: reviewed 2026 Utah DWR Hunt Planner black bear permits export. Resident, nonresident, and total columns are split for library use. Blank numeric cells mean no published numeric permit count in the reviewed source; BR7307 is 2026 code reuse: it is now the La Sal multiseason conservation package with 4 total permits and no published resident/nonresident split, while the older La Sal limited-entry multiseason history crosswalks to current BR7326.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="6">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Hunt Name</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Hunt Code</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Hunt Type</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Res</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Non-Res</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="38.1" customHeight="1" s="6">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Black Bear - Statewide Permit</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>BR1000</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Statewide</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Any open season on any open bear unit during the 2026 season. See 2026 Black Bear Guidebook for season dates take methods.</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="12" t="inlineStr"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="n"/>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="38.1" customHeight="1" s="6">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Black Bear Harvest Objective Units</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>BR1001</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Harvest Objective</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Visit wildlife.utah.gov/bearharvest for units &amp; closures. You are required to complete the annual bear orientation course &amp; carry proof while hunting bear. Visit wildlife.utah.gov/bear for details.</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
-      <c r="J5" s="14" t="inlineStr"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="38.1" customHeight="1" s="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Black Bear Pursuit - Resident</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>BR1007</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Pursuit</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Spring: Mar 28-May 25, 2026 | Summer: July 5-July 31, 2026 | Fall: Nov 2-8, 2026</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="12" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="38.1" customHeight="1" s="6">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>BR1008</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="38.1" customHeight="1" s="6">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>BR1009</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="38.1" customHeight="1" s="6">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>BR1010</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="38.1" customHeight="1" s="6">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>BR1011</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="38.1" customHeight="1" s="6">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>BR1012</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="38.1" customHeight="1" s="6">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>BR1013</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="38.1" customHeight="1" s="6">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>BR1015</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="38.1" customHeight="1" s="6">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>BR1016</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="38.1" customHeight="1" s="6">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>BR1017</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="38.1" customHeight="1" s="6">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Black Bear Pursuit - Nonresident</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>BR1018</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Pursuit</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Spring: Mar 29-May 26, 2025 | Summer: July 5 - Aug 3, 2025 | Fall: Nov 3-9, 2025</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="38.1" customHeight="1" s="6">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>BR7000</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K17" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="K17" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="N17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="38.1" customHeight="1" s="6">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>BR7001</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="K18" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="K18" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="38.1" customHeight="1" s="6">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>BR7003</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="K19" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="K19" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="M19" s="13" t="inlineStr"/>
-      <c r="N19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="38.1" customHeight="1" s="6">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>BR7004</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K20" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="K20" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr"/>
-      <c r="N20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="38.1" customHeight="1" s="6">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>BR7005</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="14" t="n">
+      <c r="J21" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K21" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
+      <c r="K21" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr"/>
-      <c r="N21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="38.1" customHeight="1" s="6">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>BR7007</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="K22" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="13" t="inlineStr"/>
-      <c r="N22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="38.1" customHeight="1" s="6">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>BR7009</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="J23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="K23" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="13" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="N23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="38.1" customHeight="1" s="6">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>BR7010</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K24" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="K24" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="N24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="38.1" customHeight="1" s="6">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BR7011</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="J25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K25" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="K25" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="13" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="N25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="38.1" customHeight="1" s="6">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>BR7012</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K26" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="K26" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr"/>
-      <c r="N26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="38.1" customHeight="1" s="6">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>BR7013</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K27" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
+      <c r="K27" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M27" s="13" t="inlineStr"/>
-      <c r="N27" s="13" t="inlineStr"/>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="38.1" customHeight="1" s="6">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>BR7014</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="K28" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L28" s="13" t="inlineStr">
+      <c r="K28" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M28" s="13" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="N28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="38.1" customHeight="1" s="6">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>BR7015</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="14" t="n">
+      <c r="J29" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K29" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="K29" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="38.1" customHeight="1" s="6">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>BR7016</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="H30" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="J30" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K30" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
+      <c r="K30" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M30" s="13" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N30" s="13" t="inlineStr"/>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="N30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="38.1" customHeight="1" s="6">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>BR7017</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="14" t="n">
+      <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="14" t="n">
+      <c r="J31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
+      <c r="K31" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M31" s="13" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N31" s="13" t="inlineStr"/>
-    </row>
-    <row r="32" ht="38" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="N31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="38.1" customHeight="1" s="6">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>BR7018</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="H32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="J32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="K32" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="N32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="38.1" customHeight="1" s="6">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BR7020</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H33" s="14" t="n">
+      <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="14" t="n">
+      <c r="I33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="14" t="n">
+      <c r="J33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
+      <c r="K33" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="13" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr"/>
-    </row>
-    <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="N33" s="3" t="n"/>
+    </row>
+    <row r="34" ht="38.1" customHeight="1" s="6">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>BR7021</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="J34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-    </row>
-    <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="38.1" customHeight="1" s="6">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BR7022</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I35" s="14" t="n">
+      <c r="I35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="14" t="n">
+      <c r="J35" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="13" t="n"/>
-    </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="38.1" customHeight="1" s="6">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>BR7100</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H36" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="J36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L36" s="13" t="inlineStr">
+      <c r="K36" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M36" s="13" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N36" s="13" t="inlineStr"/>
-    </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="N36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="38.1" customHeight="1" s="6">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>BR7101</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="H37" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="I37" s="14" t="n">
+      <c r="I37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="14" t="n">
+      <c r="J37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K37" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L37" s="13" t="inlineStr">
+      <c r="K37" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="13" t="inlineStr"/>
-    </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="38.1" customHeight="1" s="6">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>BR7102</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="J38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K38" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L38" s="13" t="inlineStr">
+      <c r="K38" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M38" s="13" t="inlineStr"/>
-      <c r="N38" s="13" t="inlineStr"/>
-    </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="38.1" customHeight="1" s="6">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>BR7104</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H39" s="14" t="n">
+      <c r="H39" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I39" s="14" t="n">
+      <c r="I39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="14" t="n">
+      <c r="J39" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K39" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
+      <c r="K39" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="13" t="inlineStr"/>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="38.1" customHeight="1" s="6">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>BR7105</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H40" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="J40" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K40" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
+      <c r="K40" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="M40" s="13" t="inlineStr"/>
-      <c r="N40" s="13" t="inlineStr"/>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
+    </row>
+    <row r="41" ht="38.1" customHeight="1" s="6">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>BR7106</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H41" s="14" t="n">
+      <c r="H41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="14" t="n">
+      <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="K41" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
+      <c r="K41" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="M41" s="13" t="inlineStr"/>
-      <c r="N41" s="13" t="inlineStr"/>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="38.1" customHeight="1" s="6">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>BR7109</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="H42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="J42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L42" s="13" t="inlineStr">
+      <c r="K42" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M42" s="13" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N42" s="13" t="inlineStr"/>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="N42" s="3" t="n"/>
+    </row>
+    <row r="43" ht="38.1" customHeight="1" s="6">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>BR7110</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="I43" s="14" t="n">
+      <c r="I43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="14" t="n">
+      <c r="J43" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K43" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
+      <c r="K43" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M43" s="13" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N43" s="13" t="inlineStr"/>
-    </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="N43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="38.1" customHeight="1" s="6">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>BR7111</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="H44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="J44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
+      <c r="K44" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M44" s="13" t="inlineStr"/>
-      <c r="N44" s="13" t="inlineStr"/>
-    </row>
-    <row r="45" ht="38" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+    </row>
+    <row r="45" ht="38.1" customHeight="1" s="6">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>BR7112</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H45" s="14" t="n">
+      <c r="H45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I45" s="14" t="n">
+      <c r="I45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="14" t="n">
+      <c r="J45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K45" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L45" s="13" t="inlineStr">
+      <c r="K45" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="M45" s="13" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N45" s="13" t="inlineStr"/>
-    </row>
-    <row r="46" ht="38" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="N45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="38.1" customHeight="1" s="6">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>BR7113</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="J46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L46" s="13" t="inlineStr">
+      <c r="K46" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="13" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N46" s="13" t="inlineStr"/>
-    </row>
-    <row r="47" ht="38" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="N46" s="3" t="n"/>
+    </row>
+    <row r="47" ht="38.1" customHeight="1" s="6">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>BR7114</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H47" s="14" t="n">
+      <c r="H47" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="I47" s="14" t="n">
+      <c r="I47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="14" t="n">
+      <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K47" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
+      <c r="K47" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M47" s="13" t="inlineStr"/>
-      <c r="N47" s="13" t="inlineStr"/>
-    </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="38.1" customHeight="1" s="6">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>BR7115</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="H48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="J48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K48" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L48" s="13" t="inlineStr">
+      <c r="K48" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="M48" s="13" t="inlineStr"/>
-      <c r="N48" s="13" t="inlineStr"/>
-    </row>
-    <row r="49" ht="38" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
+    </row>
+    <row r="49" ht="38.1" customHeight="1" s="6">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>BR7116</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H49" s="14" t="n">
+      <c r="H49" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I49" s="14" t="n">
+      <c r="I49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="14" t="n">
+      <c r="J49" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K49" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
+      <c r="K49" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="M49" s="13" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N49" s="13" t="inlineStr"/>
-    </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="N49" s="3" t="n"/>
+    </row>
+    <row r="50" ht="38.1" customHeight="1" s="6">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>BR7117</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="H50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="J50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K50" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L50" s="13" t="inlineStr">
+      <c r="K50" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="M50" s="13" t="inlineStr"/>
-      <c r="N50" s="13" t="inlineStr"/>
-    </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
+    </row>
+    <row r="51" ht="38.1" customHeight="1" s="6">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>BR7118</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H51" s="14" t="n">
+      <c r="H51" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="14" t="n">
+      <c r="I51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K51" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L51" s="13" t="inlineStr">
+      <c r="K51" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M51" s="13" t="inlineStr"/>
-      <c r="N51" s="13" t="inlineStr"/>
-    </row>
-    <row r="52" ht="38" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+    </row>
+    <row r="52" ht="38.1" customHeight="1" s="6">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>BR7119</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="H52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="J52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K52" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L52" s="13" t="inlineStr">
+      <c r="K52" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="M52" s="13" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N52" s="13" t="inlineStr"/>
-    </row>
-    <row r="53" ht="38" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="N52" s="3" t="n"/>
+    </row>
+    <row r="53" ht="38.1" customHeight="1" s="6">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>BR7120</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H53" s="14" t="n">
+      <c r="H53" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I53" s="14" t="n">
+      <c r="I53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="14" t="n">
+      <c r="J53" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K53" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
+      <c r="K53" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="M53" s="13" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N53" s="13" t="inlineStr"/>
-    </row>
-    <row r="54" ht="38" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="N53" s="3" t="n"/>
+    </row>
+    <row r="54" ht="38.1" customHeight="1" s="6">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>BR7121</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="H54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="J54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L54" s="13" t="inlineStr">
+      <c r="K54" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M54" s="13" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N54" s="13" t="inlineStr"/>
-    </row>
-    <row r="55" ht="38" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="N54" s="3" t="n"/>
+    </row>
+    <row r="55" ht="38.1" customHeight="1" s="6">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>BR7122</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H55" s="14" t="n">
+      <c r="H55" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I55" s="14" t="n">
+      <c r="I55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="14" t="n">
+      <c r="J55" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K55" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L55" s="13" t="inlineStr">
+      <c r="K55" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M55" s="13" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="N55" s="13" t="inlineStr"/>
-    </row>
-    <row r="56" ht="38" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="N55" s="3" t="n"/>
+    </row>
+    <row r="56" ht="38.1" customHeight="1" s="6">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>BR7123</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="H56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="J56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K56" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L56" s="13" t="inlineStr">
+      <c r="K56" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="M56" s="13" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N56" s="13" t="inlineStr"/>
-    </row>
-    <row r="57" ht="38" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="N56" s="3" t="n"/>
+    </row>
+    <row r="57" ht="38.1" customHeight="1" s="6">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>BR7124</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H57" s="14" t="n">
+      <c r="H57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="14" t="n">
+      <c r="I57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="14" t="n">
+      <c r="J57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L57" s="13" t="inlineStr">
+      <c r="K57" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M57" s="13" t="inlineStr"/>
-      <c r="N57" s="13" t="inlineStr"/>
-    </row>
-    <row r="58" ht="38" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+    </row>
+    <row r="58" ht="38.1" customHeight="1" s="6">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>BR7125</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="H58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="J58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K58" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L58" s="13" t="inlineStr">
+      <c r="K58" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M58" s="13" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N58" s="13" t="inlineStr"/>
-    </row>
-    <row r="59" ht="38" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="N58" s="3" t="n"/>
+    </row>
+    <row r="59" ht="38.1" customHeight="1" s="6">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>BR7126</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H59" s="14" t="n">
+      <c r="H59" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I59" s="14" t="n">
+      <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="14" t="n">
+      <c r="J59" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K59" s="13" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
-      <c r="N59" s="13" t="n"/>
-    </row>
-    <row r="60" ht="38" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="38.1" customHeight="1" s="6">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>BR7127</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="H60" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="I60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="J60" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="K60" s="13" t="n"/>
-      <c r="L60" s="13" t="n"/>
-      <c r="M60" s="13" t="n"/>
-      <c r="N60" s="13" t="n"/>
-    </row>
-    <row r="61" ht="38" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="n"/>
+    </row>
+    <row r="61" ht="38.1" customHeight="1" s="6">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>BR7200</t>
         </is>
       </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H61" s="14" t="n">
+      <c r="H61" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I61" s="14" t="n">
+      <c r="I61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="14" t="n">
+      <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K61" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L61" s="13" t="inlineStr">
+      <c r="K61" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="M61" s="13" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N61" s="13" t="inlineStr"/>
-    </row>
-    <row r="62" ht="38" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="N61" s="3" t="n"/>
+    </row>
+    <row r="62" ht="38.1" customHeight="1" s="6">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>BR7201</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 14, 2026 &amp; Oct. 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="H62" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="I62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="J62" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K62" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L62" s="13" t="inlineStr">
+      <c r="K62" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M62" s="13" t="inlineStr"/>
-      <c r="N62" s="13" t="inlineStr"/>
-    </row>
-    <row r="63" ht="38" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+    </row>
+    <row r="63" ht="38.1" customHeight="1" s="6">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>BR7203</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E63" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H63" s="14" t="n">
+      <c r="H63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I63" s="14" t="n">
+      <c r="I63" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="14" t="n">
+      <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="K63" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L63" s="13" t="inlineStr">
+      <c r="K63" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="13" t="inlineStr"/>
-    </row>
-    <row r="64" ht="38" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="38.1" customHeight="1" s="6">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>BR7204</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="H64" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="I64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="J64" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K64" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L64" s="13" t="inlineStr">
+      <c r="K64" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="13" t="inlineStr"/>
-    </row>
-    <row r="65" ht="38" customHeight="1">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="M64" s="3" t="n"/>
+      <c r="N64" s="3" t="n"/>
+    </row>
+    <row r="65" ht="38.1" customHeight="1" s="6">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>BR7205</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H65" s="14" t="n">
+      <c r="H65" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="14" t="n">
+      <c r="I65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="14" t="n">
+      <c r="J65" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K65" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L65" s="13" t="inlineStr">
+      <c r="K65" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M65" s="13" t="inlineStr"/>
-      <c r="N65" s="13" t="inlineStr"/>
-    </row>
-    <row r="66" ht="38" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
+    </row>
+    <row r="66" ht="38.1" customHeight="1" s="6">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>BR7207</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="H66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="J66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K66" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L66" s="13" t="inlineStr">
+      <c r="K66" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M66" s="13" t="inlineStr"/>
-      <c r="N66" s="13" t="inlineStr"/>
-    </row>
-    <row r="67" ht="38" customHeight="1">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="M66" s="3" t="n"/>
+      <c r="N66" s="3" t="n"/>
+    </row>
+    <row r="67" ht="38.1" customHeight="1" s="6">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>BR7210</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H67" s="14" t="n">
+      <c r="H67" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="14" t="n">
+      <c r="I67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="14" t="n">
+      <c r="J67" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K67" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
+      <c r="K67" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M67" s="13" t="inlineStr">
+      <c r="M67" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N67" s="13" t="inlineStr"/>
-    </row>
-    <row r="68" ht="38" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="N67" s="3" t="n"/>
+    </row>
+    <row r="68" ht="38.1" customHeight="1" s="6">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>BR7211</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H68" s="12" t="n">
+      <c r="H68" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="I68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="J68" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="K68" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L68" s="13" t="inlineStr">
+      <c r="K68" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M68" s="13" t="inlineStr">
+      <c r="M68" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N68" s="13" t="inlineStr"/>
-    </row>
-    <row r="69" ht="38" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
+      <c r="N68" s="3" t="n"/>
+    </row>
+    <row r="69" ht="38.1" customHeight="1" s="6">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B69" s="14" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>BR7212</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H69" s="14" t="n">
+      <c r="H69" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="14" t="n">
+      <c r="I69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="14" t="n">
+      <c r="J69" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K69" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L69" s="13" t="inlineStr">
+      <c r="K69" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M69" s="13" t="inlineStr"/>
-      <c r="N69" s="13" t="inlineStr"/>
-    </row>
-    <row r="70" ht="38" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
+    </row>
+    <row r="70" ht="38.1" customHeight="1" s="6">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>BR7213</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="H70" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I70" s="12" t="n">
+      <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="J70" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K70" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
+      <c r="K70" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="M70" s="13" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N70" s="13" t="inlineStr"/>
-    </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
+      <c r="N70" s="3" t="n"/>
+    </row>
+    <row r="71" ht="38.1" customHeight="1" s="6">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>BR7214</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F71" s="14" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G71" s="14" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H71" s="14" t="n">
+      <c r="H71" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="14" t="n">
+      <c r="I71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="14" t="n">
+      <c r="J71" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K71" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L71" s="13" t="inlineStr">
+      <c r="K71" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M71" s="13" t="inlineStr">
+      <c r="M71" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N71" s="13" t="inlineStr"/>
-    </row>
-    <row r="72" ht="38" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="N71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="38.1" customHeight="1" s="6">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>BR7215</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="H72" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I72" s="12" t="n">
+      <c r="I72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="12" t="n">
+      <c r="J72" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K72" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L72" s="13" t="inlineStr">
+      <c r="K72" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M72" s="13" t="inlineStr"/>
-      <c r="N72" s="13" t="inlineStr"/>
-    </row>
-    <row r="73" ht="38" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+    </row>
+    <row r="73" ht="38.1" customHeight="1" s="6">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>BR7216</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G73" s="14" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H73" s="14" t="n">
+      <c r="H73" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="14" t="n">
+      <c r="I73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="14" t="n">
+      <c r="J73" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K73" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L73" s="13" t="inlineStr">
+      <c r="K73" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="M73" s="13" t="inlineStr"/>
-      <c r="N73" s="13" t="inlineStr"/>
-    </row>
-    <row r="74" ht="38" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="M73" s="3" t="n"/>
+      <c r="N73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="38.1" customHeight="1" s="6">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>BR7217</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H74" s="12" t="n">
+      <c r="H74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="J74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K74" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L74" s="13" t="inlineStr">
+      <c r="K74" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M74" s="13" t="inlineStr">
+      <c r="M74" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N74" s="13" t="inlineStr"/>
-    </row>
-    <row r="75" ht="38" customHeight="1">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="N74" s="3" t="n"/>
+    </row>
+    <row r="75" ht="38.1" customHeight="1" s="6">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>BR7218</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H75" s="14" t="n">
+      <c r="H75" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I75" s="14" t="n">
+      <c r="I75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="14" t="n">
+      <c r="J75" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K75" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L75" s="13" t="inlineStr">
+      <c r="K75" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="13" t="inlineStr"/>
-    </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="M75" s="3" t="n"/>
+      <c r="N75" s="3" t="n"/>
+    </row>
+    <row r="76" ht="38.1" customHeight="1" s="6">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>BR7219</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H76" s="12" t="n">
+      <c r="H76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I76" s="12" t="n">
+      <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="J76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L76" s="13" t="inlineStr">
+      <c r="K76" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M76" s="13" t="inlineStr"/>
-      <c r="N76" s="13" t="inlineStr"/>
-    </row>
-    <row r="77" ht="38" customHeight="1">
-      <c r="A77" s="14" t="inlineStr">
+      <c r="M76" s="3" t="n"/>
+      <c r="N76" s="3" t="n"/>
+    </row>
+    <row r="77" ht="38.1" customHeight="1" s="6">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>BR7220</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H77" s="14" t="n">
+      <c r="H77" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I77" s="14" t="n">
+      <c r="I77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="14" t="n">
+      <c r="J77" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="K77" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L77" s="13" t="inlineStr">
+      <c r="K77" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M77" s="13" t="inlineStr">
+      <c r="M77" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N77" s="13" t="inlineStr"/>
-    </row>
-    <row r="78" ht="38" customHeight="1">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="N77" s="3" t="n"/>
+    </row>
+    <row r="78" ht="38.1" customHeight="1" s="6">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>BR7221</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="H78" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="12" t="n">
+      <c r="J78" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K78" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L78" s="13" t="inlineStr">
+      <c r="K78" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="M78" s="13" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N78" s="13" t="inlineStr"/>
-    </row>
-    <row r="79" ht="38" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="N78" s="3" t="n"/>
+    </row>
+    <row r="79" ht="38.1" customHeight="1" s="6">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>BR7224</t>
         </is>
       </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E79" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H79" s="14" t="n">
+      <c r="H79" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="I79" s="14" t="n">
+      <c r="I79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J79" s="14" t="n">
+      <c r="J79" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K79" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L79" s="13" t="inlineStr">
+      <c r="K79" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M79" s="13" t="inlineStr"/>
-      <c r="N79" s="13" t="inlineStr"/>
-    </row>
-    <row r="80" ht="38" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
+    </row>
+    <row r="80" ht="38.1" customHeight="1" s="6">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>BR7225</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Spot and Stalk</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Sept. 1 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L80" s="13" t="inlineStr">
+      <c r="K80" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M80" s="13" t="inlineStr"/>
-      <c r="N80" s="13" t="inlineStr"/>
-    </row>
-    <row r="81" ht="38" customHeight="1">
-      <c r="A81" s="14" t="inlineStr">
+      <c r="M80" s="3" t="n"/>
+      <c r="N80" s="3" t="n"/>
+    </row>
+    <row r="81" ht="38.1" customHeight="1" s="6">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>BR7228</t>
         </is>
       </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F81" s="14" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G81" s="14" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H81" s="14" t="n">
+      <c r="H81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="14" t="n">
+      <c r="I81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="14" t="n">
+      <c r="J81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K81" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L81" s="13" t="inlineStr">
+      <c r="K81" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M81" s="13" t="inlineStr">
+      <c r="M81" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N81" s="13" t="inlineStr"/>
-    </row>
-    <row r="82" ht="38" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="N81" s="3" t="n"/>
+    </row>
+    <row r="82" ht="38.1" customHeight="1" s="6">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>BR7229</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H82" s="12" t="n">
+      <c r="H82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="12" t="n">
+      <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="J82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K82" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L82" s="13" t="inlineStr">
+      <c r="K82" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M82" s="13" t="inlineStr">
+      <c r="M82" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N82" s="13" t="inlineStr"/>
-    </row>
-    <row r="83" ht="38" customHeight="1">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="N82" s="3" t="n"/>
+    </row>
+    <row r="83" ht="38.1" customHeight="1" s="6">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>BR7237</t>
         </is>
       </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G83" s="14" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H83" s="14" t="n">
+      <c r="H83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I83" s="14" t="n">
+      <c r="I83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="14" t="n">
+      <c r="J83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K83" s="13" t="n"/>
-      <c r="L83" s="13" t="n"/>
-      <c r="M83" s="13" t="n"/>
-      <c r="N83" s="13" t="n"/>
-    </row>
-    <row r="84" ht="38" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3" t="n"/>
+    </row>
+    <row r="84" ht="38.1" customHeight="1" s="6">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>BR7238</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H84" s="12" t="n">
+      <c r="H84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="12" t="n">
+      <c r="J84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="13" t="n"/>
-      <c r="L84" s="13" t="n"/>
-      <c r="M84" s="13" t="n"/>
-      <c r="N84" s="13" t="n"/>
-    </row>
-    <row r="85" ht="38" customHeight="1">
-      <c r="A85" s="14" t="inlineStr">
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="N84" s="3" t="n"/>
+    </row>
+    <row r="85" ht="38.1" customHeight="1" s="6">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B85" s="14" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>BR7239</t>
         </is>
       </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F85" s="14" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G85" s="14" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H85" s="14" t="n">
+      <c r="H85" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I85" s="14" t="n">
+      <c r="I85" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="14" t="n">
+      <c r="J85" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K85" s="13" t="n"/>
-      <c r="L85" s="13" t="n"/>
-      <c r="M85" s="13" t="n"/>
-      <c r="N85" s="13" t="n"/>
-    </row>
-    <row r="86" ht="38" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+      <c r="M85" s="3" t="n"/>
+      <c r="N85" s="3" t="n"/>
+    </row>
+    <row r="86" ht="38.1" customHeight="1" s="6">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>BR7300</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F86" s="12" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 14 &amp; Aug. 15 - Oct. 1 &amp; Oct. 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H86" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J86" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K86" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L86" s="13" t="inlineStr">
+      <c r="K86" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="M86" s="13" t="inlineStr"/>
-      <c r="N86" s="13" t="inlineStr"/>
-    </row>
-    <row r="87" ht="38" customHeight="1">
-      <c r="A87" s="14" t="inlineStr">
+      <c r="M86" s="3" t="n"/>
+      <c r="N86" s="3" t="n"/>
+    </row>
+    <row r="87" ht="38.1" customHeight="1" s="6">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B87" s="14" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>BR7301</t>
         </is>
       </c>
-      <c r="C87" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D87" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F87" s="14" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G87" s="14" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Sept. 1 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H87" s="14" t="n">
+      <c r="H87" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I87" s="14" t="n">
+      <c r="I87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="14" t="n">
+      <c r="J87" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K87" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L87" s="13" t="inlineStr">
+      <c r="K87" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M87" s="13" t="inlineStr"/>
-      <c r="N87" s="13" t="inlineStr"/>
-    </row>
-    <row r="88" ht="38" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="M87" s="3" t="n"/>
+      <c r="N87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="38.1" customHeight="1" s="6">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>BR7303</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H88" s="12" t="n">
+      <c r="H88" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I88" s="12" t="n">
+      <c r="I88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="12" t="n">
+      <c r="J88" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K88" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L88" s="13" t="inlineStr">
+      <c r="K88" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M88" s="13" t="inlineStr"/>
-      <c r="N88" s="13" t="inlineStr"/>
-    </row>
-    <row r="89" ht="38" customHeight="1">
-      <c r="A89" s="14" t="inlineStr">
+      <c r="M88" s="3" t="n"/>
+      <c r="N88" s="3" t="n"/>
+    </row>
+    <row r="89" ht="38.1" customHeight="1" s="6">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>BR7304</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F89" s="14" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G89" s="14" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H89" s="14" t="n">
+      <c r="H89" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="I89" s="14" t="n">
+      <c r="I89" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J89" s="14" t="n">
+      <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K89" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L89" s="13" t="inlineStr">
+      <c r="K89" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="M89" s="13" t="inlineStr"/>
-      <c r="N89" s="13" t="inlineStr"/>
-    </row>
-    <row r="90" ht="38" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="M89" s="3" t="n"/>
+      <c r="N89" s="3" t="n"/>
+    </row>
+    <row r="90" ht="38.1" customHeight="1" s="6">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>BR7305</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H90" s="12" t="n">
+      <c r="H90" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I90" s="12" t="n">
+      <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="J90" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K90" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L90" s="13" t="inlineStr">
+      <c r="K90" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M90" s="13" t="inlineStr"/>
-      <c r="N90" s="13" t="inlineStr"/>
-    </row>
-    <row r="91" ht="38" customHeight="1">
-      <c r="A91" s="14" t="inlineStr">
+      <c r="M90" s="3" t="n"/>
+      <c r="N90" s="3" t="n"/>
+    </row>
+    <row r="91" ht="38.1" customHeight="1" s="6">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>BR7307</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E91" s="14" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F91" s="14" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>Multiseason - Conservation</t>
         </is>
       </c>
-      <c r="G91" s="14" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H91" s="14" t="inlineStr"/>
-      <c r="I91" s="14" t="inlineStr"/>
-      <c r="J91" s="14" t="n">
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="n"/>
+      <c r="J91" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K91" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L91" s="13" t="inlineStr">
+      <c r="K91" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M91" s="13" t="inlineStr"/>
-      <c r="N91" s="13" t="inlineStr"/>
-    </row>
-    <row r="92" ht="38" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="M91" s="3" t="n"/>
+      <c r="N91" s="3" t="n"/>
+    </row>
+    <row r="92" ht="38.1" customHeight="1" s="6">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>BR7308</t>
         </is>
       </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H92" s="12" t="n">
+      <c r="H92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="12" t="n">
+      <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="12" t="n">
+      <c r="J92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L92" s="13" t="inlineStr">
+      <c r="K92" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M92" s="13" t="inlineStr"/>
-      <c r="N92" s="13" t="inlineStr"/>
-    </row>
-    <row r="93" ht="38" customHeight="1">
-      <c r="A93" s="14" t="inlineStr">
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
+    </row>
+    <row r="93" ht="38.1" customHeight="1" s="6">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B93" s="14" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>BR7309</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F93" s="14" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H93" s="14" t="n">
+      <c r="H93" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I93" s="14" t="n">
+      <c r="I93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="14" t="n">
+      <c r="J93" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K93" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L93" s="13" t="inlineStr">
+      <c r="K93" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M93" s="13" t="inlineStr"/>
-      <c r="N93" s="13" t="inlineStr"/>
-    </row>
-    <row r="94" ht="38" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="M93" s="3" t="n"/>
+      <c r="N93" s="3" t="n"/>
+    </row>
+    <row r="94" ht="38.1" customHeight="1" s="6">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>BR7310</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H94" s="12" t="n">
+      <c r="H94" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I94" s="12" t="n">
+      <c r="I94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="J94" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K94" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L94" s="13" t="inlineStr">
+      <c r="K94" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="M94" s="13" t="inlineStr"/>
-      <c r="N94" s="13" t="inlineStr"/>
-    </row>
-    <row r="95" ht="38" customHeight="1">
-      <c r="A95" s="14" t="inlineStr">
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
+    </row>
+    <row r="95" ht="38.1" customHeight="1" s="6">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B95" s="14" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>BR7311</t>
         </is>
       </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F95" s="14" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G95" s="14" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H95" s="14" t="n">
+      <c r="H95" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I95" s="14" t="n">
+      <c r="I95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="14" t="n">
+      <c r="J95" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L95" s="13" t="inlineStr">
+      <c r="K95" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M95" s="13" t="inlineStr"/>
-      <c r="N95" s="13" t="inlineStr"/>
-    </row>
-    <row r="96" ht="38" customHeight="1">
-      <c r="A96" s="12" t="inlineStr">
+      <c r="M95" s="3" t="n"/>
+      <c r="N95" s="3" t="n"/>
+    </row>
+    <row r="96" ht="38.1" customHeight="1" s="6">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>BR7312</t>
         </is>
       </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F96" s="12" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H96" s="12" t="n">
+      <c r="H96" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I96" s="12" t="n">
+      <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="12" t="n">
+      <c r="J96" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K96" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L96" s="13" t="inlineStr">
+      <c r="K96" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M96" s="13" t="inlineStr"/>
-      <c r="N96" s="13" t="inlineStr"/>
-    </row>
-    <row r="97" ht="38" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="M96" s="3" t="n"/>
+      <c r="N96" s="3" t="n"/>
+    </row>
+    <row r="97" ht="38.1" customHeight="1" s="6">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>BR7313</t>
         </is>
       </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E97" s="14" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F97" s="14" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G97" s="14" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H97" s="14" t="n">
+      <c r="H97" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I97" s="14" t="n">
+      <c r="I97" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="14" t="n">
+      <c r="J97" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K97" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L97" s="13" t="inlineStr">
+      <c r="K97" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M97" s="13" t="inlineStr"/>
-      <c r="N97" s="13" t="inlineStr"/>
-    </row>
-    <row r="98" ht="38" customHeight="1">
-      <c r="A98" s="12" t="inlineStr">
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
+    </row>
+    <row r="98" ht="38.1" customHeight="1" s="6">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>BR7314</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F98" s="12" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G98" s="12" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="12" t="n">
+      <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="J98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K98" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L98" s="13" t="inlineStr">
+      <c r="K98" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M98" s="13" t="inlineStr"/>
-      <c r="N98" s="13" t="inlineStr"/>
-    </row>
-    <row r="99" ht="38" customHeight="1">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="M98" s="3" t="n"/>
+      <c r="N98" s="3" t="n"/>
+    </row>
+    <row r="99" ht="38.1" customHeight="1" s="6">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>BR7315</t>
         </is>
       </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F99" s="14" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G99" s="14" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H99" s="14" t="n">
+      <c r="H99" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I99" s="14" t="n">
+      <c r="I99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="14" t="n">
+      <c r="J99" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L99" s="13" t="inlineStr">
+      <c r="K99" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M99" s="13" t="inlineStr"/>
-      <c r="N99" s="13" t="inlineStr"/>
-    </row>
-    <row r="100" ht="38" customHeight="1">
-      <c r="A100" s="12" t="inlineStr">
+      <c r="M99" s="3" t="n"/>
+      <c r="N99" s="3" t="n"/>
+    </row>
+    <row r="100" ht="38.1" customHeight="1" s="6">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>BR7316</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G100" s="12" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H100" s="12" t="n">
+      <c r="H100" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I100" s="12" t="n">
+      <c r="I100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="12" t="n">
+      <c r="J100" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K100" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L100" s="13" t="inlineStr">
+      <c r="K100" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M100" s="13" t="inlineStr"/>
-      <c r="N100" s="13" t="inlineStr"/>
-    </row>
-    <row r="101" ht="38" customHeight="1">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="M100" s="3" t="n"/>
+      <c r="N100" s="3" t="n"/>
+    </row>
+    <row r="101" ht="38.1" customHeight="1" s="6">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>BR7317</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E101" s="14" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F101" s="14" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G101" s="14" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H101" s="14" t="n">
+      <c r="H101" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I101" s="14" t="n">
+      <c r="I101" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="14" t="n">
+      <c r="J101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K101" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L101" s="13" t="inlineStr">
+      <c r="K101" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M101" s="13" t="inlineStr"/>
-      <c r="N101" s="13" t="inlineStr"/>
-    </row>
-    <row r="102" ht="38" customHeight="1">
-      <c r="A102" s="12" t="inlineStr">
+      <c r="M101" s="3" t="n"/>
+      <c r="N101" s="3" t="n"/>
+    </row>
+    <row r="102" ht="38.1" customHeight="1" s="6">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>BR7318</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F102" s="12" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G102" s="12" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="H102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I102" s="12" t="n">
+      <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="J102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K102" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L102" s="13" t="inlineStr">
+      <c r="K102" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M102" s="13" t="inlineStr"/>
-      <c r="N102" s="13" t="inlineStr"/>
-    </row>
-    <row r="103" ht="38" customHeight="1">
-      <c r="A103" s="14" t="inlineStr">
+      <c r="M102" s="3" t="n"/>
+      <c r="N102" s="3" t="n"/>
+    </row>
+    <row r="103" ht="38.1" customHeight="1" s="6">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B103" s="14" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>BR7320</t>
         </is>
       </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F103" s="14" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G103" s="14" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H103" s="14" t="n">
+      <c r="H103" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I103" s="14" t="n">
+      <c r="I103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="14" t="n">
+      <c r="J103" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K103" s="13" t="n">
+      <c r="K103" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="L103" s="13" t="inlineStr">
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M103" s="13" t="inlineStr"/>
-      <c r="N103" s="13" t="inlineStr"/>
-    </row>
-    <row r="104" ht="38" customHeight="1">
-      <c r="A104" s="12" t="inlineStr">
+      <c r="M103" s="3" t="n"/>
+      <c r="N103" s="3" t="n"/>
+    </row>
+    <row r="104" ht="38.1" customHeight="1" s="6">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>BR7321</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F104" s="12" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G104" s="12" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H104" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="I104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="J104" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K104" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L104" s="13" t="inlineStr">
+      <c r="K104" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M104" s="13" t="inlineStr"/>
-      <c r="N104" s="13" t="inlineStr"/>
-    </row>
-    <row r="105" ht="38" customHeight="1">
-      <c r="A105" s="14" t="inlineStr">
+      <c r="M104" s="3" t="n"/>
+      <c r="N104" s="3" t="n"/>
+    </row>
+    <row r="105" ht="38.1" customHeight="1" s="6">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B105" s="14" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>BR7322</t>
         </is>
       </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D105" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F105" s="14" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G105" s="14" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H105" s="14" t="n">
+      <c r="H105" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I105" s="14" t="n">
+      <c r="I105" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="14" t="n">
+      <c r="J105" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K105" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L105" s="13" t="inlineStr">
+      <c r="K105" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M105" s="13" t="inlineStr"/>
-      <c r="N105" s="13" t="inlineStr"/>
-    </row>
-    <row r="106" ht="38" customHeight="1">
-      <c r="A106" s="12" t="inlineStr">
+      <c r="M105" s="3" t="n"/>
+      <c r="N105" s="3" t="n"/>
+    </row>
+    <row r="106" ht="38.1" customHeight="1" s="6">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>BR7323</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D106" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F106" s="12" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G106" s="12" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="H106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="12" t="n">
+      <c r="J106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K106" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L106" s="13" t="inlineStr">
+      <c r="K106" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M106" s="13" t="inlineStr"/>
-      <c r="N106" s="13" t="inlineStr"/>
-    </row>
-    <row r="107" ht="38" customHeight="1">
-      <c r="A107" s="14" t="inlineStr">
+      <c r="M106" s="3" t="n"/>
+      <c r="N106" s="3" t="n"/>
+    </row>
+    <row r="107" ht="38.1" customHeight="1" s="6">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B107" s="14" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>BR7324</t>
         </is>
       </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E107" s="14" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F107" s="14" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G107" s="14" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>March 29 - May 26, 2025 | Jul 5 - 31, 2025 | Aug 1 - 31, 2025 | Sept 1 - Oct 26, 2025 | Nov 3 - 9, 2025 | Sept 1 - Oct 26, 2025</t>
         </is>
       </c>
-      <c r="H107" s="14" t="inlineStr"/>
-      <c r="I107" s="14" t="inlineStr"/>
-      <c r="J107" s="14" t="inlineStr"/>
-      <c r="K107" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L107" s="13" t="inlineStr">
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M107" s="13" t="inlineStr"/>
-      <c r="N107" s="13" t="inlineStr"/>
-    </row>
-    <row r="108" ht="38" customHeight="1">
-      <c r="A108" s="12" t="inlineStr">
+      <c r="M107" s="3" t="n"/>
+      <c r="N107" s="3" t="n"/>
+    </row>
+    <row r="108" ht="38.1" customHeight="1" s="6">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>BR7325</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D108" s="12" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F108" s="12" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G108" s="12" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K108" s="13" t="n"/>
-      <c r="L108" s="13" t="n"/>
-      <c r="M108" s="13" t="n"/>
-      <c r="N108" s="13" t="n"/>
-    </row>
-    <row r="109" ht="38" customHeight="1">
-      <c r="A109" s="14" t="inlineStr">
+      <c r="K108" s="3" t="n"/>
+      <c r="L108" s="3" t="n"/>
+      <c r="M108" s="3" t="n"/>
+      <c r="N108" s="3" t="n"/>
+    </row>
+    <row r="109" ht="38.1" customHeight="1" s="6">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B109" s="14" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>BR7326</t>
         </is>
       </c>
-      <c r="C109" s="14" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D109" s="14" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E109" s="14" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F109" s="14" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G109" s="14" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H109" s="14" t="n">
+      <c r="H109" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="I109" s="14" t="n">
+      <c r="I109" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="14" t="n">
+      <c r="J109" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K109" s="13" t="n"/>
-      <c r="L109" s="13" t="n"/>
-      <c r="M109" s="13" t="n"/>
-      <c r="N109" s="13" t="n"/>
+      <c r="K109" s="3" t="n"/>
+      <c r="L109" s="3" t="n"/>
+      <c r="M109" s="3" t="n"/>
+      <c r="N109" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:N109"/>
@@ -6559,7 +6514,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>

--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BLACK_BEAR.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BLACK_BEAR.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_BLACK_BEAR'!$A$3:$N$109</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026_BLACK_BEAR'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026_BLACK_BEAR'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +49,31 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F1B0F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005B3A25"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -77,8 +100,38 @@
         <fgColor rgb="FF4F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F2D1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5EFE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -101,11 +154,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,6 +192,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -203,7 +315,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HUNT_TABLE_BLACK_BEAR" displayName="HUNT_TABLE_BLACK_BEAR" ref="A3:N109" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HUNT_TABLE_005" displayName="HUNT_TABLE_005" ref="A3:N109" headerRowCount="1">
   <autoFilter ref="A3:N109"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Hunt Name"/>
@@ -517,5995 +629,6001 @@
   <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" style="6" min="1" max="1"/>
-    <col width="14" customWidth="1" style="6" min="2" max="4"/>
-    <col width="20" customWidth="1" style="6" min="5" max="5"/>
-    <col width="28" customWidth="1" style="6" min="6" max="6"/>
-    <col width="36" customWidth="1" style="6" min="7" max="7"/>
-    <col width="14" customWidth="1" style="6" min="8" max="10"/>
-    <col width="20" customWidth="1" style="6" min="11" max="11"/>
-    <col width="36" customWidth="1" style="6" min="12" max="14"/>
+    <col width="24" customWidth="1" style="6" min="1" max="1"/>
+    <col width="10" customWidth="1" style="6" min="2" max="4"/>
+    <col width="10" customWidth="1" style="6" min="3" max="3"/>
+    <col width="10" customWidth="1" style="6" min="4" max="4"/>
+    <col width="14" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20" customWidth="1" style="6" min="6" max="6"/>
+    <col width="24" customWidth="1" style="6" min="7" max="7"/>
+    <col width="10" customWidth="1" style="6" min="8" max="10"/>
+    <col width="10" customWidth="1" style="6" min="9" max="9"/>
+    <col width="10" customWidth="1" style="6" min="10" max="10"/>
+    <col width="14" customWidth="1" style="6" min="11" max="11"/>
+    <col width="24" customWidth="1" style="6" min="12" max="14"/>
+    <col width="24" customWidth="1" style="6" min="13" max="13"/>
+    <col width="24" customWidth="1" style="6" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" s="6">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="6">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>2026 BLACK BEAR</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.95" customHeight="1" s="6">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="40" customHeight="1" s="6">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Source: reviewed 2026 Utah DWR Hunt Planner black bear permits export. Resident, nonresident, and total columns are split for library use. Blank numeric cells mean no published numeric permit count in the reviewed source; BR7307 is 2026 code reuse: it is now the La Sal multiseason conservation package with 4 total permits and no published resident/nonresident split, while the older La Sal limited-entry multiseason history crosswalks to current BR7326.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="6">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Hunt Name</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Hunt Code</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>Hunt Type</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>Res</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Non-Res</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38.1" customHeight="1" s="6">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Black Bear - Statewide Permit</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>BR1000</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Statewide</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Any open season on any open bear unit during the 2026 season. See 2026 Black Bear Guidebook for season dates take methods.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="L4" s="20" t="n"/>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="20" t="n"/>
     </row>
     <row r="5" ht="38.1" customHeight="1" s="6">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Black Bear Harvest Objective Units</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>BR1001</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Harvest Objective</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Visit wildlife.utah.gov/bearharvest for units &amp; closures. You are required to complete the annual bear orientation course &amp; carry proof while hunting bear. Visit wildlife.utah.gov/bear for details.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
     </row>
     <row r="6" ht="38.1" customHeight="1" s="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Black Bear Pursuit - Resident</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>BR1007</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Pursuit</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>Spring: Mar 28-May 25, 2026 | Summer: July 5-July 31, 2026 | Fall: Nov 2-8, 2026</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="19" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="n"/>
     </row>
     <row r="7" ht="38.1" customHeight="1" s="6">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>BR1008</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="22" t="n">
         <v>28</v>
       </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
     </row>
     <row r="8" ht="38.1" customHeight="1" s="6">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>BR1009</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="20" t="n"/>
     </row>
     <row r="9" ht="38.1" customHeight="1" s="6">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>BR1010</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Summer</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>July 5 - 16, 2026</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
     </row>
     <row r="10" ht="38.1" customHeight="1" s="6">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>BR1011</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
     </row>
     <row r="11" ht="38.1" customHeight="1" s="6">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>BR1012</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
     </row>
     <row r="12" ht="38.1" customHeight="1" s="6">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>BR1013</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Late Summer</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>July 18 - July 31, 2026</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
     </row>
     <row r="13" ht="38.1" customHeight="1" s="6">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>BR1015</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
     </row>
     <row r="14" ht="38.1" customHeight="1" s="6">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>BR1016</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="20" t="n"/>
     </row>
     <row r="15" ht="38.1" customHeight="1" s="6">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>BR1017</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>Restricted Pursuit - Spring</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
     </row>
     <row r="16" ht="38.1" customHeight="1" s="6">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Black Bear Pursuit - Nonresident</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>BR1018</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Pursuit Only</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Pursuit</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>Spring: Mar 29-May 26, 2025 | Summer: July 5 - Aug 3, 2025 | Fall: Nov 3-9, 2025</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
     </row>
     <row r="17" ht="38.1" customHeight="1" s="6">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>BR7000</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K17" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="22" t="n"/>
     </row>
     <row r="18" ht="38.1" customHeight="1" s="6">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>BR7001</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="K18" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="20" t="n"/>
     </row>
     <row r="19" ht="38.1" customHeight="1" s="6">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>BR7003</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="K19" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
     </row>
     <row r="20" ht="38.1" customHeight="1" s="6">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>BR7004</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="K20" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="20" t="n"/>
     </row>
     <row r="21" ht="38.1" customHeight="1" s="6">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>BR7005</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="K21" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
     </row>
     <row r="22" ht="38.1" customHeight="1" s="6">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>BR7007</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="K22" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+      <c r="M22" s="20" t="n"/>
+      <c r="N22" s="20" t="n"/>
     </row>
     <row r="23" ht="38.1" customHeight="1" s="6">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>BR7009</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="K23" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n"/>
+      <c r="N23" s="22" t="n"/>
     </row>
     <row r="24" ht="38.1" customHeight="1" s="6">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>BR7010</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="K24" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="20" t="n"/>
     </row>
     <row r="25" ht="38.1" customHeight="1" s="6">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>BR7011</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="K25" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n"/>
+      <c r="N25" s="22" t="n"/>
     </row>
     <row r="26" ht="38.1" customHeight="1" s="6">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>BR7012</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="K26" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="M26" s="20" t="n"/>
+      <c r="N26" s="20" t="n"/>
     </row>
     <row r="27" ht="38.1" customHeight="1" s="6">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>BR7013</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="K27" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
     </row>
     <row r="28" ht="38.1" customHeight="1" s="6">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>BR7014</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="K28" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="20" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N28" s="3" t="n"/>
+      <c r="N28" s="20" t="n"/>
     </row>
     <row r="29" ht="38.1" customHeight="1" s="6">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>BR7015</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="K29" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
     </row>
     <row r="30" ht="38.1" customHeight="1" s="6">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>BR7016</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="K30" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="K30" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M30" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N30" s="3" t="n"/>
+      <c r="N30" s="20" t="n"/>
     </row>
     <row r="31" ht="38.1" customHeight="1" s="6">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>BR7017</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="K31" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" s="22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" s="22" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n"/>
+      <c r="N31" s="22" t="n"/>
     </row>
     <row r="32" ht="38.1" customHeight="1" s="6">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>BR7018</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="K32" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="20" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="20" t="n"/>
     </row>
     <row r="33" ht="38.1" customHeight="1" s="6">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>BR7020</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="K33" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="22" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N33" s="3" t="n"/>
+      <c r="N33" s="22" t="n"/>
     </row>
     <row r="34" ht="38.1" customHeight="1" s="6">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>BR7021</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+      <c r="K34" s="19" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="20" t="n"/>
     </row>
     <row r="35" ht="38.1" customHeight="1" s="6">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>BR7022</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="K35" s="21" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
     </row>
     <row r="36" ht="38.1" customHeight="1" s="6">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>BR7100</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="K36" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M36" s="20" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="20" t="n"/>
     </row>
     <row r="37" ht="38.1" customHeight="1" s="6">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>BR7101</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="K37" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="K37" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
     </row>
     <row r="38" ht="38.1" customHeight="1" s="6">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>BR7102</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="K38" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
+      <c r="M38" s="20" t="n"/>
+      <c r="N38" s="20" t="n"/>
     </row>
     <row r="39" ht="38.1" customHeight="1" s="6">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>BR7104</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="K39" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
     </row>
     <row r="40" ht="38.1" customHeight="1" s="6">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>BR7105</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="K40" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="M40" s="20" t="n"/>
+      <c r="N40" s="20" t="n"/>
     </row>
     <row r="41" ht="38.1" customHeight="1" s="6">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>BR7106</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="K41" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="K41" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
     </row>
     <row r="42" ht="38.1" customHeight="1" s="6">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>BR7109</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="K42" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M42" s="20" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N42" s="3" t="n"/>
+      <c r="N42" s="20" t="n"/>
     </row>
     <row r="43" ht="38.1" customHeight="1" s="6">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>BR7110</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="K43" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L43" s="22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="M43" s="22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N43" s="3" t="n"/>
+      <c r="N43" s="22" t="n"/>
     </row>
     <row r="44" ht="38.1" customHeight="1" s="6">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>BR7111</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="K44" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+      <c r="M44" s="20" t="n"/>
+      <c r="N44" s="20" t="n"/>
     </row>
     <row r="45" ht="38.1" customHeight="1" s="6">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>BR7112</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K45" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="K45" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L45" s="22" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="M45" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N45" s="3" t="n"/>
+      <c r="N45" s="22" t="n"/>
     </row>
     <row r="46" ht="38.1" customHeight="1" s="6">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>BR7113</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="K46" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="M46" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N46" s="3" t="n"/>
+      <c r="N46" s="20" t="n"/>
     </row>
     <row r="47" ht="38.1" customHeight="1" s="6">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>BR7114</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="I47" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="J47" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="K47" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="K47" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L47" s="22" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
     </row>
     <row r="48" ht="38.1" customHeight="1" s="6">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>BR7115</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="K48" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="K48" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
+      <c r="M48" s="20" t="n"/>
+      <c r="N48" s="20" t="n"/>
     </row>
     <row r="49" ht="38.1" customHeight="1" s="6">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>BR7116</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I49" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="K49" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="K49" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L49" s="22" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="M49" s="22" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N49" s="3" t="n"/>
+      <c r="N49" s="22" t="n"/>
     </row>
     <row r="50" ht="38.1" customHeight="1" s="6">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>BR7117</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K50" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="K50" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
+      <c r="M50" s="20" t="n"/>
+      <c r="N50" s="20" t="n"/>
     </row>
     <row r="51" ht="38.1" customHeight="1" s="6">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>BR7118</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K51" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="K51" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L51" s="22" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
     </row>
     <row r="52" ht="38.1" customHeight="1" s="6">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>BR7119</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K52" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="K52" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M52" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N52" s="3" t="n"/>
+      <c r="N52" s="20" t="n"/>
     </row>
     <row r="53" ht="38.1" customHeight="1" s="6">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>BR7120</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="J53" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="K53" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="K53" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L53" s="22" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M53" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N53" s="3" t="n"/>
+      <c r="N53" s="22" t="n"/>
     </row>
     <row r="54" ht="38.1" customHeight="1" s="6">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>BR7121</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="K54" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M54" s="20" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N54" s="3" t="n"/>
+      <c r="N54" s="20" t="n"/>
     </row>
     <row r="55" ht="38.1" customHeight="1" s="6">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>BR7122</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="I55" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="J55" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="K55" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="K55" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L55" s="22" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="M55" s="22" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="N55" s="3" t="n"/>
+      <c r="N55" s="22" t="n"/>
     </row>
     <row r="56" ht="38.1" customHeight="1" s="6">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>BR7123</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="K56" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
+      <c r="M56" s="20" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N56" s="3" t="n"/>
+      <c r="N56" s="20" t="n"/>
     </row>
     <row r="57" ht="38.1" customHeight="1" s="6">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>BR7124</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="K57" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L57" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
+      <c r="M57" s="22" t="n"/>
+      <c r="N57" s="22" t="n"/>
     </row>
     <row r="58" ht="38.1" customHeight="1" s="6">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>BR7125</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K58" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
+      <c r="K58" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L58" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="M58" s="20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N58" s="3" t="n"/>
+      <c r="N58" s="20" t="n"/>
     </row>
     <row r="59" ht="38.1" customHeight="1" s="6">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>BR7126</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="21" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K59" s="3" t="n"/>
-      <c r="L59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
     </row>
     <row r="60" ht="38.1" customHeight="1" s="6">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>BR7127</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Summer</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
         <is>
           <t>May 25 - June 28, 2026</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I60" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
+      <c r="K60" s="19" t="n"/>
+      <c r="L60" s="20" t="n"/>
+      <c r="M60" s="20" t="n"/>
+      <c r="N60" s="20" t="n"/>
     </row>
     <row r="61" ht="38.1" customHeight="1" s="6">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="21" t="inlineStr">
         <is>
           <t>BR7200</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I61" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K61" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="K61" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L61" s="22" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M61" s="22" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="N61" s="3" t="n"/>
+      <c r="N61" s="22" t="n"/>
     </row>
     <row r="62" ht="38.1" customHeight="1" s="6">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>BR7201</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 14, 2026 &amp; Oct. 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K62" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="K62" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
+      <c r="M62" s="20" t="n"/>
+      <c r="N62" s="20" t="n"/>
     </row>
     <row r="63" ht="38.1" customHeight="1" s="6">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>BR7203</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E63" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I63" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K63" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="K63" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L63" s="22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="3" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
     </row>
     <row r="64" ht="38.1" customHeight="1" s="6">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>BR7204</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="K64" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="3" t="n"/>
+      <c r="M64" s="20" t="n"/>
+      <c r="N64" s="20" t="n"/>
     </row>
     <row r="65" ht="38.1" customHeight="1" s="6">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="21" t="inlineStr">
         <is>
           <t>BR7205</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="C65" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E65" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K65" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
+      <c r="K65" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L65" s="22" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="3" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
     </row>
     <row r="66" ht="38.1" customHeight="1" s="6">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Fillmore, Pahvant</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>BR7207</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K66" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="K66" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="3" t="n"/>
+      <c r="M66" s="20" t="n"/>
+      <c r="N66" s="20" t="n"/>
     </row>
     <row r="67" ht="38.1" customHeight="1" s="6">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="21" t="inlineStr">
         <is>
           <t>BR7210</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="C67" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E67" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="I67" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K67" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
+      <c r="K67" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L67" s="22" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="M67" s="22" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="N67" s="3" t="n"/>
+      <c r="N67" s="22" t="n"/>
     </row>
     <row r="68" ht="38.1" customHeight="1" s="6">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>BR7211</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="I68" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="K68" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="K68" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M68" s="20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N68" s="3" t="n"/>
+      <c r="N68" s="20" t="n"/>
     </row>
     <row r="69" ht="38.1" customHeight="1" s="6">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t>BR7212</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="C69" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E69" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="I69" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="J69" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K69" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="K69" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L69" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M69" s="3" t="n"/>
-      <c r="N69" s="3" t="n"/>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
     </row>
     <row r="70" ht="38.1" customHeight="1" s="6">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>BR7213</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I70" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="K70" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
+      <c r="K70" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="M70" s="20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N70" s="3" t="n"/>
+      <c r="N70" s="20" t="n"/>
     </row>
     <row r="71" ht="38.1" customHeight="1" s="6">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="21" t="inlineStr">
         <is>
           <t>BR7214</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="C71" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="I71" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="4" t="n">
+      <c r="J71" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K71" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
+      <c r="K71" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L71" s="22" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M71" s="3" t="inlineStr">
+      <c r="M71" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N71" s="3" t="n"/>
+      <c r="N71" s="22" t="n"/>
     </row>
     <row r="72" ht="38.1" customHeight="1" s="6">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>BR7215</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I72" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K72" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="K72" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
+      <c r="M72" s="20" t="n"/>
+      <c r="N72" s="20" t="n"/>
     </row>
     <row r="73" ht="38.1" customHeight="1" s="6">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>BR7216</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="C73" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G73" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="I73" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="J73" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K73" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="K73" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L73" s="22" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
     </row>
     <row r="74" ht="38.1" customHeight="1" s="6">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>BR7217</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="I74" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="K74" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
+      <c r="K74" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L74" s="20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="M74" s="20" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="N74" s="3" t="n"/>
+      <c r="N74" s="20" t="n"/>
     </row>
     <row r="75" ht="38.1" customHeight="1" s="6">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="21" t="inlineStr">
         <is>
           <t>BR7218</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G75" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="I75" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="K75" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="K75" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L75" s="22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
     </row>
     <row r="76" ht="38.1" customHeight="1" s="6">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>BR7219</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="I76" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="K76" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L76" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M76" s="3" t="n"/>
-      <c r="N76" s="3" t="n"/>
+      <c r="M76" s="20" t="n"/>
+      <c r="N76" s="20" t="n"/>
     </row>
     <row r="77" ht="38.1" customHeight="1" s="6">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>BR7220</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="C77" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E77" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G77" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="I77" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="n">
+      <c r="J77" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K77" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="K77" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L77" s="22" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M77" s="22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N77" s="3" t="n"/>
+      <c r="N77" s="22" t="n"/>
     </row>
     <row r="78" ht="38.1" customHeight="1" s="6">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>BR7221</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I78" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K78" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="K78" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M78" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N78" s="3" t="n"/>
+      <c r="N78" s="20" t="n"/>
     </row>
     <row r="79" ht="38.1" customHeight="1" s="6">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>BR7224</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E79" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Spring</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G79" s="21" t="inlineStr">
         <is>
           <t>March 28 - May 25, 2026</t>
         </is>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="I79" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J79" s="4" t="n">
+      <c r="J79" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="K79" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="K79" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L79" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M79" s="3" t="n"/>
-      <c r="N79" s="3" t="n"/>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
     </row>
     <row r="80" ht="38.1" customHeight="1" s="6">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>BR7225</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>Spot and Stalk</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="19" t="inlineStr">
         <is>
           <t>Sept. 1 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I80" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
+      <c r="K80" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L80" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
+      <c r="M80" s="20" t="n"/>
+      <c r="N80" s="20" t="n"/>
     </row>
     <row r="81" ht="38.1" customHeight="1" s="6">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>BR7228</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G81" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="I81" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="J81" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K81" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
+      <c r="K81" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L81" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M81" s="3" t="inlineStr">
+      <c r="M81" s="22" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N81" s="3" t="n"/>
+      <c r="N81" s="22" t="n"/>
     </row>
     <row r="82" ht="38.1" customHeight="1" s="6">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>BR7229</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I82" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K82" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
+      <c r="K82" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L82" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
+      <c r="M82" s="20" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="N82" s="3" t="n"/>
+      <c r="N82" s="20" t="n"/>
     </row>
     <row r="83" ht="38.1" customHeight="1" s="6">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="21" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>BR7237</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G83" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="I83" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="n"/>
+      <c r="K83" s="21" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
     </row>
     <row r="84" ht="38.1" customHeight="1" s="6">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>BR7238</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F84" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="19" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="I84" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="N84" s="3" t="n"/>
+      <c r="K84" s="19" t="n"/>
+      <c r="L84" s="20" t="n"/>
+      <c r="M84" s="20" t="n"/>
+      <c r="N84" s="20" t="n"/>
     </row>
     <row r="85" ht="38.1" customHeight="1" s="6">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="21" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="21" t="inlineStr">
         <is>
           <t>BR7239</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>Any Legal Weapon</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Fall</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G85" s="21" t="inlineStr">
         <is>
           <t>Aug. 1 - Aug. 31, 2026 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="I85" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="J85" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K85" s="3" t="n"/>
-      <c r="L85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
-      <c r="N85" s="3" t="n"/>
+      <c r="K85" s="21" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
     </row>
     <row r="86" ht="38.1" customHeight="1" s="6">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek/South</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>BR7300</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F86" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 14 &amp; Aug. 15 - Oct. 1 &amp; Oct. 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="I86" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K86" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="K86" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L86" s="20" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="M86" s="3" t="n"/>
-      <c r="N86" s="3" t="n"/>
+      <c r="M86" s="20" t="n"/>
+      <c r="N86" s="20" t="n"/>
     </row>
     <row r="87" ht="38.1" customHeight="1" s="6">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="21" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek Roadless</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>BR7301</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G87" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Sept. 1 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="I87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K87" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
+      <c r="K87" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L87" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M87" s="3" t="n"/>
-      <c r="N87" s="3" t="n"/>
+      <c r="M87" s="22" t="n"/>
+      <c r="N87" s="22" t="n"/>
     </row>
     <row r="88" ht="38.1" customHeight="1" s="6">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>Manti, North</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t>BR7303</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="C88" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="I88" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="K88" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="K88" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L88" s="20" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M88" s="3" t="n"/>
-      <c r="N88" s="3" t="n"/>
+      <c r="M88" s="20" t="n"/>
+      <c r="N88" s="20" t="n"/>
     </row>
     <row r="89" ht="38.1" customHeight="1" s="6">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="21" t="inlineStr">
         <is>
           <t>Manti, South/San Rafael, North</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" s="21" t="inlineStr">
         <is>
           <t>BR7304</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E89" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="G89" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H89" s="4" t="n">
+      <c r="H89" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="I89" s="4" t="n">
+      <c r="I89" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="J89" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="K89" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
+      <c r="K89" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L89" s="22" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="M89" s="3" t="n"/>
-      <c r="N89" s="3" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="N89" s="22" t="n"/>
     </row>
     <row r="90" ht="38.1" customHeight="1" s="6">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="19" t="inlineStr">
         <is>
           <t>BR7305</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="I90" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K90" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="K90" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L90" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
+      <c r="M90" s="20" t="n"/>
+      <c r="N90" s="20" t="n"/>
     </row>
     <row r="91" ht="38.1" customHeight="1" s="6">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="21" t="inlineStr">
         <is>
           <t>La Sal</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="21" t="inlineStr">
         <is>
           <t>BR7307</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="21" t="inlineStr">
         <is>
           <t>Multiseason - Conservation</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G91" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n">
+      <c r="H91" s="22" t="n"/>
+      <c r="I91" s="22" t="n"/>
+      <c r="J91" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K91" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="K91" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L91" s="22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M91" s="3" t="n"/>
-      <c r="N91" s="3" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
     </row>
     <row r="92" ht="38.1" customHeight="1" s="6">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>North Slope, Three Corners/West Daggett</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="19" t="inlineStr">
         <is>
           <t>BR7308</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="2" t="n">
+      <c r="I92" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
+      <c r="K92" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L92" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M92" s="3" t="n"/>
-      <c r="N92" s="3" t="n"/>
+      <c r="M92" s="20" t="n"/>
+      <c r="N92" s="20" t="n"/>
     </row>
     <row r="93" ht="38.1" customHeight="1" s="6">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="21" t="inlineStr">
         <is>
           <t>Panguitch Lake/Zion</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="21" t="inlineStr">
         <is>
           <t>BR7309</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="G93" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I93" s="4" t="n">
+      <c r="I93" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="J93" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K93" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
+      <c r="K93" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L93" s="22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M93" s="3" t="n"/>
-      <c r="N93" s="3" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
     </row>
     <row r="94" ht="38.1" customHeight="1" s="6">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="19" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>BR7310</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="I94" s="2" t="n">
+      <c r="I94" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="K94" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="K94" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L94" s="20" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="M94" s="3" t="n"/>
-      <c r="N94" s="3" t="n"/>
+      <c r="M94" s="20" t="n"/>
+      <c r="N94" s="20" t="n"/>
     </row>
     <row r="95" ht="38.1" customHeight="1" s="6">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="21" t="inlineStr">
         <is>
           <t>Fishlake/Thousand Lakes</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="21" t="inlineStr">
         <is>
           <t>BR7311</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F95" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="G95" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H95" s="4" t="n">
+      <c r="H95" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I95" s="4" t="n">
+      <c r="I95" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J95" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
+      <c r="K95" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L95" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M95" s="3" t="n"/>
-      <c r="N95" s="3" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
     </row>
     <row r="96" ht="38.1" customHeight="1" s="6">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>BR7312</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="I96" s="2" t="n">
+      <c r="I96" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="K96" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
+      <c r="K96" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L96" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M96" s="3" t="n"/>
-      <c r="N96" s="3" t="n"/>
+      <c r="M96" s="20" t="n"/>
+      <c r="N96" s="20" t="n"/>
     </row>
     <row r="97" ht="38.1" customHeight="1" s="6">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="21" t="inlineStr">
         <is>
           <t>Diamond Mtn/Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>BR7313</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E97" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="G97" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="I97" s="4" t="n">
+      <c r="I97" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J97" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K97" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
+      <c r="K97" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L97" s="22" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M97" s="3" t="n"/>
-      <c r="N97" s="3" t="n"/>
+      <c r="M97" s="22" t="n"/>
+      <c r="N97" s="22" t="n"/>
     </row>
     <row r="98" ht="38.1" customHeight="1" s="6">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>BR7314</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="I98" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="K98" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
+      <c r="K98" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L98" s="20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M98" s="3" t="n"/>
-      <c r="N98" s="3" t="n"/>
+      <c r="M98" s="20" t="n"/>
+      <c r="N98" s="20" t="n"/>
     </row>
     <row r="99" ht="38.1" customHeight="1" s="6">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="21" t="inlineStr">
         <is>
           <t>Wasatch Mtns, Avintaquin/Currant Creek</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>BR7315</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="G99" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H99" s="4" t="n">
+      <c r="H99" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I99" s="4" t="n">
+      <c r="I99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="K99" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L99" s="22" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M99" s="3" t="n"/>
-      <c r="N99" s="3" t="n"/>
+      <c r="M99" s="22" t="n"/>
+      <c r="N99" s="22" t="n"/>
     </row>
     <row r="100" ht="38.1" customHeight="1" s="6">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="19" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West-Central</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t>BR7316</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="I100" s="2" t="n">
+      <c r="I100" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="K100" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
+      <c r="K100" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L100" s="20" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M100" s="3" t="n"/>
-      <c r="N100" s="3" t="n"/>
+      <c r="M100" s="20" t="n"/>
+      <c r="N100" s="20" t="n"/>
     </row>
     <row r="101" ht="38.1" customHeight="1" s="6">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="21" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="21" t="inlineStr">
         <is>
           <t>BR7317</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F101" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="G101" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H101" s="4" t="n">
+      <c r="H101" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="I101" s="4" t="n">
+      <c r="I101" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="4" t="n">
+      <c r="J101" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K101" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="K101" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L101" s="22" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M101" s="3" t="n"/>
-      <c r="N101" s="3" t="n"/>
+      <c r="M101" s="22" t="n"/>
+      <c r="N101" s="22" t="n"/>
     </row>
     <row r="102" ht="38.1" customHeight="1" s="6">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="19" t="inlineStr">
         <is>
           <t>Beaver</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>BR7318</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I102" s="2" t="n">
+      <c r="I102" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K102" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
+      <c r="K102" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L102" s="20" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M102" s="3" t="n"/>
-      <c r="N102" s="3" t="n"/>
+      <c r="M102" s="20" t="n"/>
+      <c r="N102" s="20" t="n"/>
     </row>
     <row r="103" ht="38.1" customHeight="1" s="6">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="21" t="inlineStr">
         <is>
           <t>Cache/Ogden</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>BR7320</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E103" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F103" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G103" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H103" s="4" t="n">
+      <c r="H103" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="I103" s="4" t="n">
+      <c r="I103" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K103" s="3" t="n">
+      <c r="K103" s="21" t="n">
         <v>2023</v>
       </c>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="L103" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M103" s="3" t="n"/>
-      <c r="N103" s="3" t="n"/>
+      <c r="M103" s="22" t="n"/>
+      <c r="N103" s="22" t="n"/>
     </row>
     <row r="104" ht="38.1" customHeight="1" s="6">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="19" t="inlineStr">
         <is>
           <t>Kamas/North Slope, Summit</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>BR7321</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F104" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="I104" s="2" t="n">
+      <c r="I104" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="K104" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
+      <c r="K104" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L104" s="20" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M104" s="3" t="n"/>
-      <c r="N104" s="3" t="n"/>
+      <c r="M104" s="20" t="n"/>
+      <c r="N104" s="20" t="n"/>
     </row>
     <row r="105" ht="38.1" customHeight="1" s="6">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="21" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>BR7322</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E105" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F105" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
+      <c r="G105" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H105" s="4" t="n">
+      <c r="H105" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="I105" s="4" t="n">
+      <c r="I105" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="4" t="n">
+      <c r="J105" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K105" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="K105" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L105" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M105" s="3" t="n"/>
-      <c r="N105" s="3" t="n"/>
+      <c r="M105" s="22" t="n"/>
+      <c r="N105" s="22" t="n"/>
     </row>
     <row r="106" ht="38.1" customHeight="1" s="6">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>Paunsaugunt</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>BR7323</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I106" s="2" t="n">
+      <c r="I106" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K106" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
+      <c r="K106" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L106" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M106" s="3" t="n"/>
-      <c r="N106" s="3" t="n"/>
+      <c r="M106" s="20" t="n"/>
+      <c r="N106" s="20" t="n"/>
     </row>
     <row r="107" ht="38.1" customHeight="1" s="6">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>BR7324</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F107" s="21" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="G107" s="21" t="inlineStr">
         <is>
           <t>March 29 - May 26, 2025 | Jul 5 - 31, 2025 | Aug 1 - 31, 2025 | Sept 1 - Oct 26, 2025 | Nov 3 - 9, 2025 | Sept 1 - Oct 26, 2025</t>
         </is>
       </c>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
+      <c r="H107" s="22" t="n"/>
+      <c r="I107" s="22" t="n"/>
+      <c r="J107" s="22" t="n"/>
+      <c r="K107" s="21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L107" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M107" s="3" t="n"/>
-      <c r="N107" s="3" t="n"/>
+      <c r="M107" s="22" t="n"/>
+      <c r="N107" s="22" t="n"/>
     </row>
     <row r="108" ht="38.1" customHeight="1" s="6">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="19" t="inlineStr">
         <is>
           <t>Chalk Creek/East Canyon/Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>BR7325</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="19" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; July 5 - 31 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I108" s="2" t="n">
+      <c r="I108" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K108" s="3" t="n"/>
-      <c r="L108" s="3" t="n"/>
-      <c r="M108" s="3" t="n"/>
-      <c r="N108" s="3" t="n"/>
+      <c r="K108" s="19" t="n"/>
+      <c r="L108" s="20" t="n"/>
+      <c r="M108" s="20" t="n"/>
+      <c r="N108" s="20" t="n"/>
     </row>
     <row r="109" ht="38.1" customHeight="1" s="6">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="21" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="21" t="inlineStr">
         <is>
           <t>BR7326</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Either Sex</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Black Bear</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="C109" s="21" t="inlineStr">
+        <is>
+          <t>Either Sex</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="E109" s="21" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F109" s="21" t="inlineStr">
         <is>
           <t>Limited Entry - Multiseason</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="G109" s="21" t="inlineStr">
         <is>
           <t>Mar. 28 - May 25 &amp; May 25 - June 28 &amp; Aug. 1 - Aug. 31 &amp; Sept. 1 - Oct. 25 &amp; Nov 2 - Nov. 8, 2026</t>
         </is>
       </c>
-      <c r="H109" s="4" t="n">
+      <c r="H109" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="I109" s="4" t="n">
+      <c r="I109" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="K109" s="3" t="n"/>
-      <c r="L109" s="3" t="n"/>
-      <c r="M109" s="3" t="n"/>
-      <c r="N109" s="3" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="22" t="n"/>
+      <c r="M109" s="22" t="n"/>
+      <c r="N109" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:N109"/>
@@ -6513,8 +6631,9 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
